--- a/docs/partner/04_BrowseJobs_Whitelabel_Feature_Matrix.xlsx
+++ b/docs/partner/04_BrowseJobs_Whitelabel_Feature_Matrix.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +108,30 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000A1220"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="000000FF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000A1220"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000A1220"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="6">
@@ -157,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -205,8 +227,20 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -2142,29 +2176,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>Pricing — to be completed before issue</t>
+          <t>Pricing — list prices</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Yellow cells are the ones to fill in. Nothing in this workbook should reach a customer with a price still unset.</t>
+          <t>List prices, ex-GST, monthly on an annual commitment. Every figure here is solved in 08_..._Cost_and_Pricing_Model.xlsx — change it there first, or the margin it implies is fiction. Yellow cells are quote-specific and set per deal.</t>
         </is>
       </c>
     </row>
@@ -2181,27 +2216,32 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Platform fee (monthly, ex-GST)</t>
+          <t>Licence — India (₹/mo)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Included students</t>
+          <t>Licence — Intl ($/mo)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Included seats</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>Included AI allowance</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Overage rate</t>
-        </is>
-      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Onboarding fee</t>
+          <t>Onboarding fee (India)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Negotiated rate</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2258,30 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>₹24,999</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>$499</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>Up to 100 enrolled</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>AI Assist for 25 students · 150 voice minutes (≈10 mock interviews)</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>₹1,25,000</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>[ SET ]</t>
         </is>
@@ -2255,25 +2300,30 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>₹74,999</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>$1,499</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>Up to 500 enrolled</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>AI Assist for 100 students · 400 voice minutes (≈27 mock interviews)</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>₹1,25,000</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>[ SET ]</t>
         </is>
@@ -2292,25 +2342,30 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>₹1,99,999</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>$3,499</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>Up to 1,500 enrolled, then per seat</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>[ SET ]</t>
+          <t>AI Assist for 250 students · 800 voice minutes (≈53 mock interviews)</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>₹1,25,000</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>[ SET ]</t>
         </is>
@@ -2319,42 +2374,205 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>Metered, on top of the licence</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Meter</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>What it covers</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Intl</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>AI Assist</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Per AI-active student, per month</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Tutor, auto-grading and written mock-interview analysis.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>₹199</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>$3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>AI Voice mock</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Per minute, on our voice keys</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>A 15-minute mock interview costs about ₹375.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>₹25</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>$0.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>AI Voice mock</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Per minute, on your own Vapi/Twilio keys</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Orchestration only — you hold the vendor contract and the bill.</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>₹6</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>$0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Extra enrolled seat</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Per seat, per month, beyond the tier band</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Charged on enrolment, not on activity.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>₹35</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>$0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
           <t>Billing notes</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>• Fees are quoted exclusive of GST.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>• AI usage above the tier allowance is billed monthly in arrears against the metered record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>• Fees are quoted exclusive of GST. Indian invoices carry GST at 18%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>• Listed rates are the monthly price on an annual commitment. Month-to-month is 20% higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>• AI usage above the tier allowance is billed monthly in arrears against the metered record in ai_events — purpose, model, tokens, cost and latency, per call, per tenant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>• Voice minutes may be prepaid in blocks, or billed in arrears at the standard rate. Prepaid blocks do not expire while the subscription is live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>• Third-party costs on your own accounts — Zoom, payment gateway, WhatsApp — are never marked up by us.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>• Annual commitments are invoiced in advance; monthly plans in advance, per month.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>• The onboarding fee is one-time and is due before implementation begins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>• International pricing is billed in USD. The INR and USD price lists are independent, not an FX conversion of one another.</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2609,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>What it will do</t>
         </is>
@@ -2484,24 +2702,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Used for</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Zoom</t>
         </is>
@@ -2511,14 +2729,14 @@
           <t>Live classes, licence pooling, recordings</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Razorpay</t>
         </is>
@@ -2528,14 +2746,14 @@
           <t>Fees, instalments, receipts, webhooks</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>WhatsApp Cloud API</t>
         </is>
@@ -2545,14 +2763,14 @@
           <t>Campaigns, nudges, notifications</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Google OAuth &amp; Calendar</t>
         </is>
@@ -2562,14 +2780,14 @@
           <t>Sign-in, scheduling, Drive file store</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Voice AI (Vapi / Retell)</t>
         </is>
@@ -2579,14 +2797,14 @@
           <t>Voice mock interviews, AI screening calls</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Metered</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>LLM providers</t>
         </is>
@@ -2596,14 +2814,14 @@
           <t>Tutor, grading, syllabus, analysis — provider-switchable</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Metered</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Job feed (JSearch)</t>
         </is>
@@ -2613,14 +2831,14 @@
           <t>Live openings for the job radar</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Shared or your key</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Meta lead ads</t>
         </is>
@@ -2630,14 +2848,14 @@
           <t>Lead capture webhooks into the CRM</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Email (SMTP/IMAP)</t>
         </is>
@@ -2647,14 +2865,14 @@
           <t>Transactional mail and the CRM inbox</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>Your account</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>AWS S3</t>
         </is>
@@ -2664,7 +2882,7 @@
           <t>Document, recording and render storage</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Ours or yours</t>
         </is>
